--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,142 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>COUNTRY PARK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-07, 2026-03-09, 2026-03-11, 2026-03-15, 2026-03-16, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-09, 2026-03-15, 2026-03-16, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SKY TOWER</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-17, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-17, 2026-03-24, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PANORAMIK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ALCALA GRAN RESERVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-17, 2026-03-19, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE AURORA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE SOLEIL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-20, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TERRAZA DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-13, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BOSQUES DEL HATO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-16, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-11, 2026-03-20, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +603,15 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE MONTEVISTA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -609,8 +609,16 @@
           <t>PARQUE ORIENTE MONTEVISTA</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-11, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-16, 2026-03-27</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,17 +417,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
@@ -453,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
     </row>
@@ -470,7 +458,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-07, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-07, 2026-03-15, 2026-03-18, 2026-03-19, 2026-03-29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -487,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-07, 2026-03-09, 2026-03-11, 2026-03-15, 2026-03-16, 2026-03-18, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-15, 2026-03-16, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -504,7 +492,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-17, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-09, 2026-03-17, 2026-03-24, 2026-03-26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -521,7 +509,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -538,12 +526,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-17, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-17, 2026-03-19, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-17, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
     </row>
@@ -555,12 +543,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-06, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
     </row>
@@ -572,12 +560,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
     </row>
@@ -606,7 +594,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-20, 2026-03-25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -623,7 +611,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-16, 2026-03-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
